--- a/data/quarterly/FY26Q3_targets.xlsx
+++ b/data/quarterly/FY26Q3_targets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/bystore/data/quarterly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE72785-5085-064B-B649-2DA1FE2B91AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAFE0CD-AF44-404C-A8CA-617B77FA58BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8860" yWindow="2600" windowWidth="27840" windowHeight="16820" xr2:uid="{73983044-4198-324E-B2A3-9427D297574B}"/>
+    <workbookView xWindow="6360" yWindow="2600" windowWidth="27840" windowHeight="16820" xr2:uid="{73983044-4198-324E-B2A3-9427D297574B}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -89,15 +89,15 @@
     <t>總計</t>
   </si>
   <si>
-    <t>26Q2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>本季目標</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>上週目標</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q3</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -626,7 +626,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -640,10 +640,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">

--- a/data/quarterly/FY26Q3_targets.xlsx
+++ b/data/quarterly/FY26Q3_targets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/bystore/data/quarterly/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAFE0CD-AF44-404C-A8CA-617B77FA58BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46D2B3C-2081-0C43-915D-8FF2144E54B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6360" yWindow="2600" windowWidth="27840" windowHeight="16820" xr2:uid="{73983044-4198-324E-B2A3-9427D297574B}"/>
   </bookViews>
@@ -662,6 +662,9 @@
       <c r="C6" s="8">
         <v>330</v>
       </c>
+      <c r="D6" s="8">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A7" s="6"/>
@@ -671,6 +674,9 @@
       <c r="C7" s="8">
         <v>700</v>
       </c>
+      <c r="D7" s="8">
+        <v>75</v>
+      </c>
     </row>
     <row r="8" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A8" s="6"/>
@@ -705,6 +711,9 @@
       <c r="C11" s="8">
         <v>230</v>
       </c>
+      <c r="D11" s="8">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A12" s="6"/>
@@ -714,6 +723,9 @@
       <c r="C12" s="8">
         <v>600</v>
       </c>
+      <c r="D12" s="8">
+        <v>45</v>
+      </c>
     </row>
     <row r="13" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A13" s="6"/>
@@ -751,6 +763,9 @@
       <c r="C16" s="8">
         <v>60</v>
       </c>
+      <c r="D16" s="8">
+        <v>5</v>
+      </c>
     </row>
     <row r="17" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A17" s="6"/>
@@ -760,6 +775,9 @@
       <c r="C17" s="8">
         <v>200</v>
       </c>
+      <c r="D17" s="8">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A18" s="6"/>
@@ -797,6 +815,9 @@
       <c r="C21" s="8">
         <v>50</v>
       </c>
+      <c r="D21" s="8">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A22" s="6"/>
@@ -806,6 +827,9 @@
       <c r="C22" s="8">
         <v>185</v>
       </c>
+      <c r="D22" s="8">
+        <v>20</v>
+      </c>
     </row>
     <row r="23" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A23" s="6"/>
@@ -843,6 +867,9 @@
       <c r="C26" s="8">
         <v>60</v>
       </c>
+      <c r="D26" s="8">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
       <c r="A27" s="6"/>
@@ -851,6 +878,9 @@
       </c>
       <c r="C27" s="8">
         <v>225</v>
+      </c>
+      <c r="D27" s="8">
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="8" customFormat="1" ht="20" customHeight="1">
